--- a/data/trending_integrated_20260923_15.xlsx
+++ b/data/trending_integrated_20260923_15.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4205</v>
+        <v>4185</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+26.85%</t>
+          <t>'+26.24%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-1.02</v>
       </c>
       <c r="E2" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F2" t="n">
         <v>51</v>
       </c>
       <c r="G2" t="n">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="H2" t="n">
         <v>1.63</v>
@@ -610,7 +610,7 @@
         <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>48990278876</v>
+        <v>49982352752</v>
       </c>
       <c r="P2" t="n">
         <v>6950</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19090</v>
+        <v>18940</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+23.00%</t>
+          <t>'+22.04%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.5</v>
       </c>
       <c r="E3" t="n">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F3" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G3" t="n">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="H3" t="n">
         <v>0.6</v>
@@ -702,7 +702,7 @@
         <v>1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>125148733290</v>
+        <v>128491455390</v>
       </c>
       <c r="P3" t="n">
         <v>34650</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>NASA 선정 및 스페이스X 관련 뉴스, 11조원 시장 규모 언급 등 강력한 호재 기반의 긍정적 전망. 2만원 돌파 및 시총 1조 달성 가능성 제시.</t>
+          <t>NASA 선정 초소형 엑스레이 발생기 'Xcam6' 및 스페이스X 관련 소식. 포터블 X-Ray 시장 성장 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['NASA', '스페이스X', '엑스레이']</t>
+          <t>['NASA', '스페이스X']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1938</v>
+        <v>1920</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+20.90%</t>
+          <t>'+19.78%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.39</v>
       </c>
       <c r="E4" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F4" t="n">
         <v>61</v>
       </c>
       <c r="G4" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H4" t="n">
         <v>1.02</v>
@@ -794,7 +794,7 @@
         <v>1.41</v>
       </c>
       <c r="O4" t="n">
-        <v>64843096782</v>
+        <v>66239452554</v>
       </c>
       <c r="P4" t="n">
         <v>2465</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 특허 플렉시블 PCB 확보 및 AI 데이터센터향 공급 확대 소식 기반의 주가 상승 기대.</t>
+          <t>미국 특허 획득 및 AI 데이터센터향 공급 확대 뉴스. LG엔솔 납품 기대감 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['플렉시블 PCB', 'AI 데이터센터']</t>
+          <t>['미국 특허', 'AI 데이터센터']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,7 +827,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18200</v>
+        <v>18180</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.04%</t>
+          <t>'+9.92%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.15</v>
       </c>
       <c r="E5" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F5" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G5" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H5" t="n">
         <v>0.62</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>310871668505</v>
+        <v>312564970060</v>
       </c>
       <c r="P5" t="n">
         <v>30550</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>나라스페이스테크놀로지</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14230</v>
+        <v>14130</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.46%</t>
+          <t>'+8.44%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.42</v>
+        <v>-0.9</v>
       </c>
       <c r="E6" t="n">
-        <v>89</v>
+        <v>143</v>
       </c>
       <c r="F6" t="n">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="G6" t="n">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="H6" t="n">
-        <v>0.86</v>
+        <v>1.89</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13000</v>
+        <v>13030</v>
       </c>
       <c r="K6" t="n">
-        <v>12870</v>
+        <v>12850</v>
       </c>
       <c r="L6" t="n">
-        <v>15900</v>
+        <v>16420</v>
       </c>
       <c r="M6" t="n">
-        <v>12650</v>
+        <v>12660</v>
       </c>
       <c r="N6" t="n">
-        <v>0.44</v>
+        <v>2.79</v>
       </c>
       <c r="O6" t="n">
-        <v>170040690930</v>
+        <v>130560990605</v>
       </c>
       <c r="P6" t="n">
-        <v>25700</v>
+        <v>64600</v>
       </c>
       <c r="Q6" t="n">
-        <v>4600</v>
+        <v>7520</v>
       </c>
       <c r="R6" t="n">
-        <v>100000</v>
+        <v>-11000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-125000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2차 상승 기대감 및 단기 과열 지정 가능성 언급. 명절 전 상승 후 하락 가능성 제기.</t>
+          <t>초소형 위성 자율 근접 운영 국방과제 주관 뉴스. 우주 항공 대장주 기대감 표현.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['2차상승', '단기과열', '명절효과']</t>
+          <t>['초소형 위성', '국방 과제']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,43 +1011,43 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>072950</t>
+          <t>478340</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>나라스페이스테크놀로지</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14080</v>
+        <v>14000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.06%</t>
+          <t>'+7.69%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.9</v>
+        <v>0.42</v>
       </c>
       <c r="E7" t="n">
-        <v>142</v>
+        <v>92</v>
       </c>
       <c r="F7" t="n">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="G7" t="n">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="H7" t="n">
-        <v>1.89</v>
+        <v>0.86</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>13030</v>
+        <v>13000</v>
       </c>
       <c r="K7" t="n">
-        <v>12850</v>
+        <v>12870</v>
       </c>
       <c r="L7" t="n">
-        <v>16420</v>
+        <v>15900</v>
       </c>
       <c r="M7" t="n">
-        <v>12660</v>
+        <v>12650</v>
       </c>
       <c r="N7" t="n">
-        <v>2.79</v>
+        <v>0.44</v>
       </c>
       <c r="O7" t="n">
-        <v>129367754790</v>
+        <v>171841460150</v>
       </c>
       <c r="P7" t="n">
-        <v>64600</v>
+        <v>25700</v>
       </c>
       <c r="Q7" t="n">
-        <v>7520</v>
+        <v>4600</v>
       </c>
       <c r="R7" t="n">
-        <v>-11000</v>
+        <v>100000</v>
       </c>
       <c r="S7" t="n">
-        <v>-125000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>초소형위성 테마 관련 국방과제 주관 뉴스 및 67억원 규모 계약 내용이 있으나, 투기 과열 및 단일가 지정 관련 우려와 함께 주가 급락에 대한 불만 표출.</t>
+          <t>2차 상승 기대감 및 단기 과열 지정 가능성 언급. 명절 전 상승 후 하락 가능성 제기.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['초소형위성', '국방과제', '투기과열']</t>
+          <t>['2차상승', '단기과열', '명절효과']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,95 +1103,95 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>478340</t>
+          <t>072950</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7920</v>
+        <v>220000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.07%</t>
+          <t>'+4.02%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.42</v>
+        <v>0.01</v>
       </c>
       <c r="E8" t="n">
         <v>121</v>
       </c>
       <c r="F8" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="G8" t="n">
-        <v>365</v>
+        <v>494</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7610</v>
+        <v>211500</v>
       </c>
       <c r="K8" t="n">
-        <v>7850</v>
+        <v>217000</v>
       </c>
       <c r="L8" t="n">
-        <v>8720</v>
+        <v>220000</v>
       </c>
       <c r="M8" t="n">
-        <v>7730</v>
+        <v>216500</v>
       </c>
       <c r="N8" t="n">
-        <v>2.32</v>
+        <v>75.5</v>
       </c>
       <c r="O8" t="n">
-        <v>91751965510</v>
+        <v>1045952809750</v>
       </c>
       <c r="P8" t="n">
-        <v>16200</v>
+        <v>243500</v>
       </c>
       <c r="Q8" t="n">
-        <v>1206</v>
+        <v>65000</v>
       </c>
       <c r="R8" t="n">
-        <v>-35000</v>
+        <v>715000</v>
       </c>
       <c r="S8" t="n">
-        <v>2000</v>
+        <v>-52000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>양자 보안 테마 관련 언급 및 기대감이 있으나, 주가 계단식 하락 및 매물대 돌파 여부에 대한 불확실성 존재. 외인 매도세 정리 후 상승 가능성 언급.</t>
+          <t>배당금 확대 및 우선주 매력 부각. 장기 투자 및 30만원 돌파 기대감 표현.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['양자보안', '매물대', '외인']</t>
+          <t>['배당금', '우선주']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,99 +1200,99 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>220000</v>
+        <v>7880</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.02%</t>
+          <t>'+3.55%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.01</v>
+        <v>-0.42</v>
       </c>
       <c r="E9" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="F9" t="n">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="G9" t="n">
-        <v>489</v>
+        <v>365</v>
       </c>
       <c r="H9" t="n">
-        <v>75.51000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>211500</v>
+        <v>7610</v>
       </c>
       <c r="K9" t="n">
-        <v>217000</v>
+        <v>7850</v>
       </c>
       <c r="L9" t="n">
-        <v>220000</v>
+        <v>8720</v>
       </c>
       <c r="M9" t="n">
-        <v>216500</v>
+        <v>7730</v>
       </c>
       <c r="N9" t="n">
-        <v>75.5</v>
+        <v>2.32</v>
       </c>
       <c r="O9" t="n">
-        <v>1015228459250</v>
+        <v>92265705810</v>
       </c>
       <c r="P9" t="n">
-        <v>243500</v>
+        <v>16200</v>
       </c>
       <c r="Q9" t="n">
-        <v>65000</v>
+        <v>1206</v>
       </c>
       <c r="R9" t="n">
-        <v>715000</v>
+        <v>-35000</v>
       </c>
       <c r="S9" t="n">
-        <v>-52000</v>
+        <v>2000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>평생 보유 및 수천만원대 배당금 수령에 대한 기대감이 높음. 우선주 소각 이슈와 자사주 관련 언급이 있음.</t>
+          <t>양자 보안 테마 관련 언급 및 기대감이 있으나, 주가 계단식 하락 및 매물대 돌파 여부에 대한 불확실성 존재. 외인 매도세 정리 후 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['우선주', '배당금', '자사주']</t>
+          <t>['양자보안', '매물대', '외인']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>284000</v>
+        <v>284500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.71%</t>
+          <t>'+2.89%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G10" t="n">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="H10" t="n">
         <v>46.55</v>
@@ -1346,7 +1346,7 @@
         <v>46.56</v>
       </c>
       <c r="O10" t="n">
-        <v>4425356604750</v>
+        <v>4589361794750</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 발언 및 정치인 언급이 다수이며, 특정 가격대 돌파 및 배당 관련 언급이 있으나 근거 없는 개인적 예상 위주.</t>
+          <t>정치적 언급이 다수 포함되었으며, 일부에서는 주가 상승 기대감을 표현하나 명확한 근거 부족.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['주가 예상', '배당']</t>
+          <t>['정치', '주가 전망']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13930</v>
+        <v>13950</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.43%</t>
+          <t>'+2.57%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1438,7 +1438,7 @@
         <v>9.77</v>
       </c>
       <c r="O11" t="n">
-        <v>102007883300</v>
+        <v>102656955870</v>
       </c>
       <c r="P11" t="n">
         <v>23550</v>
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="G12" t="n">
-        <v>1669</v>
+        <v>1703</v>
       </c>
       <c r="H12" t="n">
         <v>50.15</v>
@@ -1530,7 +1530,7 @@
         <v>50.17</v>
       </c>
       <c r="O12" t="n">
-        <v>4646149567500</v>
+        <v>4759761492000</v>
       </c>
       <c r="P12" t="n">
         <v>2987000</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>환율 및 국장 전체에 대한 부정적 언급과 함께, 주가 하락에 대한 불만 및 사기 의혹 제기. 자사주 매입 외에는 상승 어렵다는 전망.</t>
+          <t>국내 증시 전반에 대한 불만과 함께 하이닉스 주가 부진에 대한 비판. ADR 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['환율', '국장', '자사주']</t>
+          <t>['국내 증시', 'ADR']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31500</v>
+        <v>8490</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.32%</t>
+          <t>'+0.24%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.62</v>
+        <v>0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>58</v>
+        <v>127</v>
       </c>
       <c r="F13" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="G13" t="n">
-        <v>169</v>
+        <v>386</v>
       </c>
       <c r="H13" t="n">
-        <v>52.81</v>
+        <v>26.63</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>31400</v>
+        <v>8470</v>
       </c>
       <c r="K13" t="n">
-        <v>31500</v>
+        <v>8510</v>
       </c>
       <c r="L13" t="n">
-        <v>32100</v>
+        <v>8870</v>
       </c>
       <c r="M13" t="n">
-        <v>31100</v>
+        <v>8470</v>
       </c>
       <c r="N13" t="n">
-        <v>25.75</v>
+        <v>26.58</v>
       </c>
       <c r="O13" t="n">
-        <v>119225052725</v>
+        <v>28692466335</v>
       </c>
       <c r="P13" t="n">
-        <v>32100</v>
+        <v>17950</v>
       </c>
       <c r="Q13" t="n">
-        <v>21000</v>
+        <v>8120</v>
       </c>
       <c r="R13" t="n">
-        <v>-81000</v>
+        <v>276000</v>
       </c>
       <c r="S13" t="n">
-        <v>219000</v>
+        <v>-68000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>인천공항 이용객 증가 및 내년 영업이익 전망 제시, 합병 효과는 장기적 관점.</t>
+          <t>키움증권의 매매 행태 및 목표주가 하향 리포트에 대한 의혹 제기. 유리 기판 사업 등 신규 사업 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['영업이익', '합병', '인천공항']</t>
+          <t>['키움증권', '유리 기판']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8480</v>
+        <v>31450</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+0.16%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.05</v>
+        <v>0.62</v>
       </c>
       <c r="E14" t="n">
-        <v>122</v>
+        <v>58</v>
       </c>
       <c r="F14" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="G14" t="n">
-        <v>382</v>
+        <v>172</v>
       </c>
       <c r="H14" t="n">
-        <v>26.63</v>
+        <v>52.78</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,91 +1699,91 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>8470</v>
+        <v>31400</v>
       </c>
       <c r="K14" t="n">
-        <v>8510</v>
+        <v>31500</v>
       </c>
       <c r="L14" t="n">
-        <v>8870</v>
+        <v>32100</v>
       </c>
       <c r="M14" t="n">
-        <v>8470</v>
+        <v>31100</v>
       </c>
       <c r="N14" t="n">
-        <v>26.58</v>
+        <v>25.75</v>
       </c>
       <c r="O14" t="n">
-        <v>28095080425</v>
+        <v>122359267325</v>
       </c>
       <c r="P14" t="n">
-        <v>17950</v>
+        <v>32100</v>
       </c>
       <c r="Q14" t="n">
-        <v>8120</v>
+        <v>21000</v>
       </c>
       <c r="R14" t="n">
-        <v>276000</v>
+        <v>-81000</v>
       </c>
       <c r="S14" t="n">
-        <v>-68000</v>
+        <v>219000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>유리 인터포저 및 게이밍 OLED 기술 부각. 실적 개선 및 목표 주가 상향 전망. 허수매도 의혹 제기.</t>
+          <t>인천공항 이용객 증가 및 내년 영업이익 전망 제시, 합병 효과는 장기적 관점.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['OLED', '유리 인터포저', '실적']</t>
+          <t>['영업이익', '합병', '인천공항']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17730</v>
+        <v>3700</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.45%</t>
+          <t>'-0.67%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.76</v>
+        <v>-0.35</v>
       </c>
       <c r="E15" t="n">
-        <v>150</v>
+        <v>183</v>
       </c>
       <c r="F15" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G15" t="n">
-        <v>933</v>
+        <v>515</v>
       </c>
       <c r="H15" t="n">
-        <v>5.46</v>
+        <v>0.61</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>17810</v>
+        <v>3725</v>
       </c>
       <c r="K15" t="n">
-        <v>17950</v>
+        <v>3740</v>
       </c>
       <c r="L15" t="n">
-        <v>18180</v>
+        <v>4200</v>
       </c>
       <c r="M15" t="n">
-        <v>17410</v>
+        <v>3665</v>
       </c>
       <c r="N15" t="n">
-        <v>6.22</v>
+        <v>0.96</v>
       </c>
       <c r="O15" t="n">
-        <v>144151404830</v>
+        <v>69374408372</v>
       </c>
       <c r="P15" t="n">
-        <v>31500</v>
+        <v>6300</v>
       </c>
       <c r="Q15" t="n">
-        <v>1272</v>
+        <v>1738</v>
       </c>
       <c r="R15" t="n">
-        <v>-273000</v>
+        <v>-176000</v>
       </c>
       <c r="S15" t="n">
-        <v>1000</v>
+        <v>-5000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>명절 전 상승 기대감 속 2만원 돌파 시도 및 주포 활동 언급. 단타 세력의 빠른 이탈 촉구.</t>
+          <t>주가 급락에 대한 불만과 종목 자체에 대한 부정적인 평가. 상폐 가능성 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['코스닥', '주포', '단타']</t>
+          <t>['주가 급락', '부정적 평가']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3700</v>
+        <v>17610</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-0.67%</t>
+          <t>'-1.12%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.35</v>
+        <v>-0.76</v>
       </c>
       <c r="E16" t="n">
-        <v>179</v>
+        <v>152</v>
       </c>
       <c r="F16" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G16" t="n">
-        <v>503</v>
+        <v>970</v>
       </c>
       <c r="H16" t="n">
-        <v>0.61</v>
+        <v>5.46</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,38 +1883,38 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>3725</v>
+        <v>17810</v>
       </c>
       <c r="K16" t="n">
-        <v>3740</v>
+        <v>17950</v>
       </c>
       <c r="L16" t="n">
-        <v>4200</v>
+        <v>18180</v>
       </c>
       <c r="M16" t="n">
-        <v>3665</v>
+        <v>17410</v>
       </c>
       <c r="N16" t="n">
-        <v>0.96</v>
+        <v>6.22</v>
       </c>
       <c r="O16" t="n">
-        <v>69109487985</v>
+        <v>146639725795</v>
       </c>
       <c r="P16" t="n">
-        <v>6300</v>
+        <v>31500</v>
       </c>
       <c r="Q16" t="n">
-        <v>1738</v>
+        <v>1272</v>
       </c>
       <c r="R16" t="n">
-        <v>-176000</v>
+        <v>-273000</v>
       </c>
       <c r="S16" t="n">
-        <v>-5000</v>
+        <v>1000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>연이은 음봉 및 급락으로 인한 투자 심리 위축. 물량 떠넘기기 및 주포의 단기 매매 의혹.</t>
+          <t>명절 전 주가 상승 기대와 함께 일부 부정적인 의견도 존재. 단타 및 광 섹터 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['단타', '물량 떠넘기기', '거래량']</t>
+          <t>['명절', '단타']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30550</v>
+        <v>30650</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.61%</t>
+          <t>'-1.29%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.21</v>
       </c>
       <c r="E17" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F17" t="n">
         <v>220</v>
       </c>
       <c r="G17" t="n">
-        <v>2271</v>
+        <v>2289</v>
       </c>
       <c r="H17" t="n">
         <v>16.63</v>
@@ -1990,7 +1990,7 @@
         <v>16.42</v>
       </c>
       <c r="O17" t="n">
-        <v>13873132750</v>
+        <v>14546061525</v>
       </c>
       <c r="P17" t="n">
         <v>69200</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30850</v>
+        <v>31000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.37%</t>
+          <t>'-1.90%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.4</v>
       </c>
       <c r="E18" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F18" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G18" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H18" t="n">
         <v>11.7</v>
@@ -2082,7 +2082,7 @@
         <v>11.3</v>
       </c>
       <c r="O18" t="n">
-        <v>82272060050</v>
+        <v>84048125925</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23100</v>
+        <v>22900</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.55%</t>
+          <t>'-4.38%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.08</v>
       </c>
       <c r="E19" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F19" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G19" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="H19" t="n">
         <v>1.68</v>
@@ -2174,7 +2174,7 @@
         <v>1.76</v>
       </c>
       <c r="O19" t="n">
-        <v>76135959025</v>
+        <v>76600186950</v>
       </c>
       <c r="P19" t="n">
         <v>39350</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>48850</v>
+        <v>48925</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.59%</t>
+          <t>'-4.44%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F20" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G20" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H20" t="n">
         <v>38.34</v>
@@ -2266,7 +2266,7 @@
         <v>38.44</v>
       </c>
       <c r="O20" t="n">
-        <v>94543184950</v>
+        <v>98297514700</v>
       </c>
       <c r="P20" t="n">
         <v>67300</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>81200</v>
+        <v>81400</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-6.13%</t>
+          <t>'-5.90%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>717</v>
+        <v>728</v>
       </c>
       <c r="F21" t="n">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="G21" t="n">
-        <v>2142</v>
+        <v>2163</v>
       </c>
       <c r="H21" t="n">
         <v>23.03</v>
@@ -2358,7 +2358,7 @@
         <v>23.05</v>
       </c>
       <c r="O21" t="n">
-        <v>338960924550</v>
+        <v>346676663600</v>
       </c>
       <c r="P21" t="n">
         <v>139200</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17305</v>
+        <v>17370</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-7.95%</t>
+          <t>'-7.61%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.09</v>
       </c>
       <c r="E22" t="n">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="F22" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G22" t="n">
-        <v>1231</v>
+        <v>1253</v>
       </c>
       <c r="H22" t="n">
         <v>10.38</v>
@@ -2450,7 +2450,7 @@
         <v>10.47</v>
       </c>
       <c r="O22" t="n">
-        <v>156543941290</v>
+        <v>158722868010</v>
       </c>
       <c r="P22" t="n">
         <v>40350</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>공매도 세력의 파산 및 마지막 저항 언급. 금융 당국 조사 관련 내용 포함.</t>
+          <t>공매도 세력에 대한 강한 비난과 파산 가능성 언급. 실질적인 주가 조작 의혹 및 조사 촉구 내용 포함.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['공매도', '대차']</t>
+          <t>['공매도', '주가 조작']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2625</v>
+        <v>2610</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-9.01%</t>
+          <t>'-9.53%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.92</v>
       </c>
       <c r="E23" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F23" t="n">
         <v>59</v>
       </c>
       <c r="G23" t="n">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="H23" t="n">
         <v>1.4</v>
@@ -2536,13 +2536,13 @@
         <v>3480</v>
       </c>
       <c r="M23" t="n">
-        <v>2597</v>
+        <v>2585</v>
       </c>
       <c r="N23" t="n">
         <v>0.48</v>
       </c>
       <c r="O23" t="n">
-        <v>23292822756</v>
+        <v>23406634371</v>
       </c>
       <c r="P23" t="n">
         <v>4760</v>

--- a/data/trending_integrated_20260923_15.xlsx
+++ b/data/trending_integrated_20260923_15.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4185</v>
+        <v>4010</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+26.24%</t>
+          <t>'+20.97%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-1.02</v>
       </c>
       <c r="E2" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G2" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="H2" t="n">
         <v>1.63</v>
@@ -610,7 +610,7 @@
         <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>49982352752</v>
+        <v>51125207171</v>
       </c>
       <c r="P2" t="n">
         <v>6950</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18940</v>
+        <v>18770</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.04%</t>
+          <t>'+20.94%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.5</v>
       </c>
       <c r="E3" t="n">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F3" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G3" t="n">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="H3" t="n">
         <v>0.6</v>
@@ -702,7 +702,7 @@
         <v>1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>128491455390</v>
+        <v>131747435320</v>
       </c>
       <c r="P3" t="n">
         <v>34650</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1920</v>
+        <v>1938</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+19.78%</t>
+          <t>'+20.90%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.39</v>
       </c>
       <c r="E4" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G4" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H4" t="n">
         <v>1.02</v>
@@ -794,7 +794,7 @@
         <v>1.41</v>
       </c>
       <c r="O4" t="n">
-        <v>66239452554</v>
+        <v>67295739156</v>
       </c>
       <c r="P4" t="n">
         <v>2465</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 특허 획득 및 AI 데이터센터향 공급 확대 뉴스. LG엔솔 납품 기대감 언급.</t>
+          <t>미국 특허 기반 AI 데이터센터향 플렉시블 PCB 공급 확대.  긍정적 뉴스 및 재료 기반 급등 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['미국 특허', 'AI 데이터센터']</t>
+          <t>['미국 특허', 'AI 데이터센터', '플렉시블 PCB']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18180</v>
+        <v>18130</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.92%</t>
+          <t>'+9.61%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.15</v>
       </c>
       <c r="E5" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F5" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G5" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H5" t="n">
         <v>0.62</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>312564970060</v>
+        <v>313639642610</v>
       </c>
       <c r="P5" t="n">
         <v>30550</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>나라스페이스테크놀로지</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14130</v>
+        <v>14170</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.44%</t>
+          <t>'+9.00%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.9</v>
+        <v>0.42</v>
       </c>
       <c r="E6" t="n">
-        <v>143</v>
+        <v>97</v>
       </c>
       <c r="F6" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="G6" t="n">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="H6" t="n">
-        <v>1.89</v>
+        <v>0.86</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13030</v>
+        <v>13000</v>
       </c>
       <c r="K6" t="n">
-        <v>12850</v>
+        <v>12870</v>
       </c>
       <c r="L6" t="n">
-        <v>16420</v>
+        <v>15900</v>
       </c>
       <c r="M6" t="n">
-        <v>12660</v>
+        <v>12650</v>
       </c>
       <c r="N6" t="n">
-        <v>2.79</v>
+        <v>0.44</v>
       </c>
       <c r="O6" t="n">
-        <v>130560990605</v>
+        <v>173111126425</v>
       </c>
       <c r="P6" t="n">
-        <v>64600</v>
+        <v>25700</v>
       </c>
       <c r="Q6" t="n">
-        <v>7520</v>
+        <v>4600</v>
       </c>
       <c r="R6" t="n">
-        <v>-11000</v>
+        <v>100000</v>
       </c>
       <c r="S6" t="n">
-        <v>-125000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>초소형 위성 자율 근접 운영 국방과제 주관 뉴스. 우주 항공 대장주 기대감 표현.</t>
+          <t>2차 상승 기대감 및 단기 과열 지정 가능성 언급. 명절 전 상승 후 하락 가능성 제기.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['초소형 위성', '국방 과제']</t>
+          <t>['2차상승', '단기과열', '명절효과']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,43 +1011,43 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>478340</t>
+          <t>072950</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>나라스페이스테크놀로지</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14000</v>
+        <v>14130</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.69%</t>
+          <t>'+8.44%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.42</v>
+        <v>-0.9</v>
       </c>
       <c r="E7" t="n">
-        <v>92</v>
+        <v>146</v>
       </c>
       <c r="F7" t="n">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="G7" t="n">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="H7" t="n">
-        <v>0.86</v>
+        <v>1.89</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>13000</v>
+        <v>13030</v>
       </c>
       <c r="K7" t="n">
-        <v>12870</v>
+        <v>12850</v>
       </c>
       <c r="L7" t="n">
-        <v>15900</v>
+        <v>16420</v>
       </c>
       <c r="M7" t="n">
-        <v>12650</v>
+        <v>12660</v>
       </c>
       <c r="N7" t="n">
-        <v>0.44</v>
+        <v>2.79</v>
       </c>
       <c r="O7" t="n">
-        <v>171841460150</v>
+        <v>131212384800</v>
       </c>
       <c r="P7" t="n">
-        <v>25700</v>
+        <v>64600</v>
       </c>
       <c r="Q7" t="n">
-        <v>4600</v>
+        <v>7520</v>
       </c>
       <c r="R7" t="n">
-        <v>100000</v>
+        <v>-11000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-125000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2차 상승 기대감 및 단기 과열 지정 가능성 언급. 명절 전 상승 후 하락 가능성 제기.</t>
+          <t>초소형 위성 자율 근접 운영 국방과제 주관 뉴스. 우주 항공 대장주 기대감 표현.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['2차상승', '단기과열', '명절효과']</t>
+          <t>['초소형 위성', '국방 과제']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>072950</t>
+          <t>478340</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>220000</v>
+        <v>219500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.02%</t>
+          <t>'+3.78%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F8" t="n">
         <v>77</v>
       </c>
       <c r="G8" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="H8" t="n">
         <v>75.51000000000001</v>
@@ -1162,7 +1162,7 @@
         <v>75.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1045952809750</v>
+        <v>1088661410000</v>
       </c>
       <c r="P8" t="n">
         <v>243500</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>배당금 확대 및 우선주 매력 부각. 장기 투자 및 30만원 돌파 기대감 표현.</t>
+          <t>배당금 증액 및 자사주 소각 이슈 기반 장기 보유 의견.  추가 상승 여력 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['배당금', '우선주']</t>
+          <t>['배당금', '자사주 소각', '장기 보유']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1222,13 +1222,13 @@
         <v>-0.42</v>
       </c>
       <c r="E9" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F9" t="n">
         <v>58</v>
       </c>
       <c r="G9" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H9" t="n">
         <v>1.9</v>
@@ -1254,7 +1254,7 @@
         <v>2.32</v>
       </c>
       <c r="O9" t="n">
-        <v>92265705810</v>
+        <v>92639979945</v>
       </c>
       <c r="P9" t="n">
         <v>16200</v>
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="G10" t="n">
-        <v>1771</v>
+        <v>1743</v>
       </c>
       <c r="H10" t="n">
         <v>46.55</v>
@@ -1337,7 +1337,7 @@
         <v>284500</v>
       </c>
       <c r="L10" t="n">
-        <v>285000</v>
+        <v>285500</v>
       </c>
       <c r="M10" t="n">
         <v>281000</v>
@@ -1346,7 +1346,7 @@
         <v>46.56</v>
       </c>
       <c r="O10" t="n">
-        <v>4589361794750</v>
+        <v>4852049139250</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 언급이 다수 포함되었으며, 일부에서는 주가 상승 기대감을 표현하나 명확한 근거 부족.</t>
+          <t>정치 관련 발언 다수, 단기 주가 상승 기대감 존재.  실질적 호재 분석 부족.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['정치', '주가 전망']</t>
+          <t>['주가', '기대감', '호재']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13950</v>
+        <v>13960</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.57%</t>
+          <t>'+2.65%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.16</v>
       </c>
       <c r="E11" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F11" t="n">
         <v>41</v>
       </c>
       <c r="G11" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="H11" t="n">
         <v>9.609999999999999</v>
@@ -1438,7 +1438,7 @@
         <v>9.77</v>
       </c>
       <c r="O11" t="n">
-        <v>102656955870</v>
+        <v>103449536025</v>
       </c>
       <c r="P11" t="n">
         <v>23550</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1852000</v>
+        <v>1858000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.65%</t>
+          <t>'+0.98%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="G12" t="n">
-        <v>1703</v>
+        <v>1699</v>
       </c>
       <c r="H12" t="n">
         <v>50.15</v>
@@ -1530,7 +1530,7 @@
         <v>50.17</v>
       </c>
       <c r="O12" t="n">
-        <v>4759761492000</v>
+        <v>4869531095000</v>
       </c>
       <c r="P12" t="n">
         <v>2987000</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>국내 증시 전반에 대한 불만과 함께 하이닉스 주가 부진에 대한 비판. ADR 언급.</t>
+          <t>ADR 대비 부진한 주가 흐름에 대한 불만 고조.  증권사 및 정부 정책 비판.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['국내 증시', 'ADR']</t>
+          <t>['ADR', '주가 관리', '불만']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1590,13 +1590,13 @@
         <v>0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F13" t="n">
         <v>53</v>
       </c>
       <c r="G13" t="n">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H13" t="n">
         <v>26.63</v>
@@ -1622,7 +1622,7 @@
         <v>26.58</v>
       </c>
       <c r="O13" t="n">
-        <v>28692466335</v>
+        <v>29764700255</v>
       </c>
       <c r="P13" t="n">
         <v>17950</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31450</v>
+        <v>31350</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.16%</t>
+          <t>'-0.16%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1688,10 +1688,10 @@
         <v>36</v>
       </c>
       <c r="G14" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="H14" t="n">
-        <v>52.78</v>
+        <v>52.8</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>25.75</v>
       </c>
       <c r="O14" t="n">
-        <v>122359267325</v>
+        <v>124581422600</v>
       </c>
       <c r="P14" t="n">
         <v>32100</v>
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3700</v>
+        <v>17680</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.67%</t>
+          <t>'-0.73%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.35</v>
+        <v>-0.76</v>
       </c>
       <c r="E15" t="n">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="F15" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G15" t="n">
-        <v>515</v>
+        <v>992</v>
       </c>
       <c r="H15" t="n">
-        <v>0.61</v>
+        <v>5.46</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>3725</v>
+        <v>17810</v>
       </c>
       <c r="K15" t="n">
-        <v>3740</v>
+        <v>17950</v>
       </c>
       <c r="L15" t="n">
-        <v>4200</v>
+        <v>18180</v>
       </c>
       <c r="M15" t="n">
-        <v>3665</v>
+        <v>17410</v>
       </c>
       <c r="N15" t="n">
-        <v>0.96</v>
+        <v>6.22</v>
       </c>
       <c r="O15" t="n">
-        <v>69374408372</v>
+        <v>148334465410</v>
       </c>
       <c r="P15" t="n">
-        <v>6300</v>
+        <v>31500</v>
       </c>
       <c r="Q15" t="n">
-        <v>1738</v>
+        <v>1272</v>
       </c>
       <c r="R15" t="n">
-        <v>-176000</v>
+        <v>-273000</v>
       </c>
       <c r="S15" t="n">
-        <v>-5000</v>
+        <v>1000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 급락에 대한 불만과 종목 자체에 대한 부정적인 평가. 상폐 가능성 언급.</t>
+          <t>추석 연휴 전 2만원 돌파 기대감.  단기 급등 가능성 언급, 실질적 근거 부족.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가 급락', '부정적 평가']</t>
+          <t>['2만원 돌파', '기대감', '단기 급등']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17610</v>
+        <v>3685</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.12%</t>
+          <t>'-1.07%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.76</v>
+        <v>-0.35</v>
       </c>
       <c r="E16" t="n">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="F16" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G16" t="n">
-        <v>970</v>
+        <v>525</v>
       </c>
       <c r="H16" t="n">
-        <v>5.46</v>
+        <v>0.61</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>17810</v>
+        <v>3725</v>
       </c>
       <c r="K16" t="n">
-        <v>17950</v>
+        <v>3740</v>
       </c>
       <c r="L16" t="n">
-        <v>18180</v>
+        <v>4200</v>
       </c>
       <c r="M16" t="n">
-        <v>17410</v>
+        <v>3665</v>
       </c>
       <c r="N16" t="n">
-        <v>6.22</v>
+        <v>0.96</v>
       </c>
       <c r="O16" t="n">
-        <v>146639725795</v>
+        <v>69676250665</v>
       </c>
       <c r="P16" t="n">
-        <v>31500</v>
+        <v>6300</v>
       </c>
       <c r="Q16" t="n">
-        <v>1272</v>
+        <v>1738</v>
       </c>
       <c r="R16" t="n">
-        <v>-273000</v>
+        <v>-176000</v>
       </c>
       <c r="S16" t="n">
-        <v>1000</v>
+        <v>-5000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>명절 전 주가 상승 기대와 함께 일부 부정적인 의견도 존재. 단타 및 광 섹터 언급.</t>
+          <t>주가 급락에 대한 불만과 종목 자체에 대한 부정적인 평가. 상폐 가능성 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['명절', '단타']</t>
+          <t>['주가 급락', '부정적 평가']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30650</v>
+        <v>30550</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.29%</t>
+          <t>'-1.61%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.21</v>
       </c>
       <c r="E17" t="n">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="F17" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G17" t="n">
-        <v>2289</v>
+        <v>2391</v>
       </c>
       <c r="H17" t="n">
         <v>16.63</v>
@@ -1990,7 +1990,7 @@
         <v>16.42</v>
       </c>
       <c r="O17" t="n">
-        <v>14546061525</v>
+        <v>15465662025</v>
       </c>
       <c r="P17" t="n">
         <v>69200</v>
@@ -2082,7 +2082,7 @@
         <v>11.3</v>
       </c>
       <c r="O18" t="n">
-        <v>84048125925</v>
+        <v>86051745175</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2127,70 +2127,70 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22900</v>
+        <v>49300</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.38%</t>
+          <t>'-3.71%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="E19" t="n">
         <v>113</v>
       </c>
       <c r="F19" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="G19" t="n">
-        <v>151</v>
+        <v>228</v>
       </c>
       <c r="H19" t="n">
-        <v>1.68</v>
+        <v>38.34</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>23950</v>
+        <v>51200</v>
       </c>
       <c r="K19" t="n">
-        <v>24400</v>
+        <v>51600</v>
       </c>
       <c r="L19" t="n">
-        <v>25700</v>
+        <v>51600</v>
       </c>
       <c r="M19" t="n">
-        <v>22700</v>
+        <v>48600</v>
       </c>
       <c r="N19" t="n">
-        <v>1.76</v>
+        <v>38.44</v>
       </c>
       <c r="O19" t="n">
-        <v>76600186950</v>
+        <v>101803624175</v>
       </c>
       <c r="P19" t="n">
-        <v>39350</v>
+        <v>67300</v>
       </c>
       <c r="Q19" t="n">
-        <v>8200</v>
+        <v>23150</v>
       </c>
       <c r="R19" t="n">
-        <v>-50000</v>
+        <v>-432000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>타임지 선정 헬스테크 기업 언급, 저조한 거래량 속 상승 기대감 있으나 매도세 관찰됨.</t>
+          <t>삼성 E&amp;A의 주가 하락에 대한 불만 표현. 20일선 지지 실패 및 6개월 보유 기간에 대한 회의감.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['헬스테크', '타임지', '거래량']</t>
+          <t>['20일선', '주가 하락', 'MSCI']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,77 +2212,77 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>48925</v>
+        <v>22950</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.44%</t>
+          <t>'-4.18%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="E20" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F20" t="n">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="G20" t="n">
-        <v>226</v>
+        <v>158</v>
       </c>
       <c r="H20" t="n">
-        <v>38.34</v>
+        <v>1.68</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>51200</v>
+        <v>23950</v>
       </c>
       <c r="K20" t="n">
-        <v>51600</v>
+        <v>24400</v>
       </c>
       <c r="L20" t="n">
-        <v>51600</v>
+        <v>25700</v>
       </c>
       <c r="M20" t="n">
-        <v>48600</v>
+        <v>22700</v>
       </c>
       <c r="N20" t="n">
-        <v>38.44</v>
+        <v>1.76</v>
       </c>
       <c r="O20" t="n">
-        <v>98297514700</v>
+        <v>77051378500</v>
       </c>
       <c r="P20" t="n">
-        <v>67300</v>
+        <v>39350</v>
       </c>
       <c r="Q20" t="n">
-        <v>23150</v>
+        <v>8200</v>
       </c>
       <c r="R20" t="n">
-        <v>-432000</v>
+        <v>-50000</v>
       </c>
       <c r="S20" t="n">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>삼성 E&amp;A의 주가 하락에 대한 불만 표현. 20일선 지지 실패 및 6개월 보유 기간에 대한 회의감.</t>
+          <t>타임지 선정 헬스테크 기업 언급, 저조한 거래량 속 상승 기대감 있으나 매도세 관찰됨.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['20일선', '주가 하락', 'MSCI']</t>
+          <t>['헬스테크', '타임지', '거래량']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>81400</v>
+        <v>81700</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.90%</t>
+          <t>'-5.55%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>728</v>
+        <v>737</v>
       </c>
       <c r="F21" t="n">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="G21" t="n">
-        <v>2163</v>
+        <v>2182</v>
       </c>
       <c r="H21" t="n">
         <v>23.03</v>
@@ -2358,7 +2358,7 @@
         <v>23.05</v>
       </c>
       <c r="O21" t="n">
-        <v>346676663600</v>
+        <v>355574628900</v>
       </c>
       <c r="P21" t="n">
         <v>139200</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 원전 수주 관련 뉴스가 있으나, 재료 소멸 및 주가 하락에 대한 부정적 전망이 우세하며, 차트 분석 및 회사 부도 징조 언급.</t>
+          <t>미국형 원전 수주 관련 긍정적 뉴스에도 불구하고 주가 하락세.  재료 소멸 및 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', '수주', '재료 소멸']</t>
+          <t>['원전 수주', '재료 소멸', '주가 하락']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17370</v>
+        <v>17440</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-7.61%</t>
+          <t>'-7.23%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.09</v>
       </c>
       <c r="E22" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="F22" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G22" t="n">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="H22" t="n">
         <v>10.38</v>
@@ -2450,7 +2450,7 @@
         <v>10.47</v>
       </c>
       <c r="O22" t="n">
-        <v>158722868010</v>
+        <v>160963690185</v>
       </c>
       <c r="P22" t="n">
         <v>40350</v>
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2610</v>
+        <v>2605</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-9.53%</t>
+          <t>'-9.71%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2516,7 +2516,7 @@
         <v>59</v>
       </c>
       <c r="G23" t="n">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="H23" t="n">
         <v>1.4</v>
@@ -2536,13 +2536,13 @@
         <v>3480</v>
       </c>
       <c r="M23" t="n">
-        <v>2585</v>
+        <v>2575</v>
       </c>
       <c r="N23" t="n">
         <v>0.48</v>
       </c>
       <c r="O23" t="n">
-        <v>23406634371</v>
+        <v>23504235006</v>
       </c>
       <c r="P23" t="n">
         <v>4760</v>

--- a/data/trending_integrated_20260923_15.xlsx
+++ b/data/trending_integrated_20260923_15.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4010</v>
+        <v>4060</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+20.97%</t>
+          <t>'+22.47%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -581,10 +581,10 @@
         <v>96</v>
       </c>
       <c r="F2" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H2" t="n">
         <v>1.63</v>
@@ -610,7 +610,7 @@
         <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>51125207171</v>
+        <v>51299222831</v>
       </c>
       <c r="P2" t="n">
         <v>6950</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18770</v>
+        <v>18850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.94%</t>
+          <t>'+21.46%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.5</v>
       </c>
       <c r="E3" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F3" t="n">
         <v>92</v>
       </c>
       <c r="G3" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="H3" t="n">
         <v>0.6</v>
@@ -702,7 +702,7 @@
         <v>1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>131747435320</v>
+        <v>132392802770</v>
       </c>
       <c r="P3" t="n">
         <v>34650</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1938</v>
+        <v>1936</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+20.90%</t>
+          <t>'+20.77%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.39</v>
       </c>
       <c r="E4" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F4" t="n">
         <v>62</v>
       </c>
       <c r="G4" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H4" t="n">
         <v>1.02</v>
@@ -794,7 +794,7 @@
         <v>1.41</v>
       </c>
       <c r="O4" t="n">
-        <v>67295739156</v>
+        <v>67544255732</v>
       </c>
       <c r="P4" t="n">
         <v>2465</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 특허 기반 AI 데이터센터향 플렉시블 PCB 공급 확대.  긍정적 뉴스 및 재료 기반 급등 기대.</t>
+          <t>삼기에너지솔루션즈, 美 특허 플렉시블PCB AI 데이터센터향 공급 확대. 엔비디아 ESS 파트너 선정.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['미국 특허', 'AI 데이터센터', '플렉시블 PCB']</t>
+          <t>['플렉시블 PCB', 'AI 데이터센터', 'ESS']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18130</v>
+        <v>18220</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.61%</t>
+          <t>'+10.16%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.15</v>
       </c>
       <c r="E5" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F5" t="n">
         <v>142</v>
       </c>
       <c r="G5" t="n">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="H5" t="n">
         <v>0.62</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>313639642610</v>
+        <v>314403425010</v>
       </c>
       <c r="P5" t="n">
         <v>30550</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 양자 관련주 급등 소식과 함께, 양자 보안 테마 관련 기대감 및 공매도 관련 언급. 단기 과열 및 차트 이탈에 대한 우려도 존재.</t>
+          <t>미국 양자 관련주 급등에 따른 엑스게이트 기대감. 양자 보안 관련주 단타 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['양자보안', '공매도', '테마']</t>
+          <t>['양자 보안', '단타', '급등']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14170</v>
+        <v>14200</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.00%</t>
+          <t>'+9.23%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.42</v>
       </c>
       <c r="E6" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G6" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H6" t="n">
         <v>0.86</v>
@@ -978,7 +978,7 @@
         <v>0.44</v>
       </c>
       <c r="O6" t="n">
-        <v>173111126425</v>
+        <v>173384362825</v>
       </c>
       <c r="P6" t="n">
         <v>25700</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14130</v>
+        <v>14190</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.44%</t>
+          <t>'+8.90%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.9</v>
       </c>
       <c r="E7" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F7" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G7" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H7" t="n">
         <v>1.89</v>
@@ -1070,7 +1070,7 @@
         <v>2.79</v>
       </c>
       <c r="O7" t="n">
-        <v>131212384800</v>
+        <v>131520875400</v>
       </c>
       <c r="P7" t="n">
         <v>64600</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>219500</v>
+        <v>220000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.78%</t>
+          <t>'+4.02%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F8" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G8" t="n">
-        <v>496</v>
+        <v>531</v>
       </c>
       <c r="H8" t="n">
         <v>75.51000000000001</v>
@@ -1162,7 +1162,7 @@
         <v>75.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1088661410000</v>
+        <v>1129935170000</v>
       </c>
       <c r="P8" t="n">
         <v>243500</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>배당금 증액 및 자사주 소각 이슈 기반 장기 보유 의견.  추가 상승 여력 기대.</t>
+          <t>삼성전자우 장기 보유 및 배당금 증액 기대. 우선주 소각 이슈와 30만원 돌파 목표.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['배당금', '자사주 소각', '장기 보유']</t>
+          <t>['배당금', '우선주', '장기 보유']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7880</v>
+        <v>7910</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.55%</t>
+          <t>'+3.94%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1254,7 +1254,7 @@
         <v>2.32</v>
       </c>
       <c r="O9" t="n">
-        <v>92639979945</v>
+        <v>92792445195</v>
       </c>
       <c r="P9" t="n">
         <v>16200</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>284500</v>
+        <v>285500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.89%</t>
+          <t>'+3.25%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="G10" t="n">
-        <v>1743</v>
+        <v>1793</v>
       </c>
       <c r="H10" t="n">
         <v>46.55</v>
@@ -1346,7 +1346,7 @@
         <v>46.56</v>
       </c>
       <c r="O10" t="n">
-        <v>4852049139250</v>
+        <v>5279657049750</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치 관련 발언 다수, 단기 주가 상승 기대감 존재.  실질적 호재 분석 부족.</t>
+          <t>삼성전자 주가 30만 돌파 및 9월, 10월 예상 주가 전망. 외인 기관 쌍끌이 매수 관측.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['주가', '기대감', '호재']</t>
+          <t>['주가 전망', '외인 매수', '쌍끌이']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13960</v>
+        <v>13950</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.65%</t>
+          <t>'+2.57%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.16</v>
       </c>
       <c r="E11" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F11" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H11" t="n">
         <v>9.609999999999999</v>
@@ -1438,7 +1438,7 @@
         <v>9.77</v>
       </c>
       <c r="O11" t="n">
-        <v>103449536025</v>
+        <v>104059164975</v>
       </c>
       <c r="P11" t="n">
         <v>23550</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1858000</v>
+        <v>1862000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.98%</t>
+          <t>'+1.20%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G12" t="n">
-        <v>1699</v>
+        <v>1707</v>
       </c>
       <c r="H12" t="n">
         <v>50.15</v>
@@ -1530,7 +1530,7 @@
         <v>50.17</v>
       </c>
       <c r="O12" t="n">
-        <v>4869531095000</v>
+        <v>5211081479000</v>
       </c>
       <c r="P12" t="n">
         <v>2987000</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8490</v>
+        <v>31500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.24%</t>
+          <t>'+0.32%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.05</v>
+        <v>0.62</v>
       </c>
       <c r="E13" t="n">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="F13" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="G13" t="n">
-        <v>385</v>
+        <v>184</v>
       </c>
       <c r="H13" t="n">
-        <v>26.63</v>
+        <v>52.81</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>8470</v>
+        <v>31400</v>
       </c>
       <c r="K13" t="n">
-        <v>8510</v>
+        <v>31500</v>
       </c>
       <c r="L13" t="n">
-        <v>8870</v>
+        <v>32100</v>
       </c>
       <c r="M13" t="n">
-        <v>8470</v>
+        <v>31100</v>
       </c>
       <c r="N13" t="n">
-        <v>26.58</v>
+        <v>25.75</v>
       </c>
       <c r="O13" t="n">
-        <v>29764700255</v>
+        <v>127118999600</v>
       </c>
       <c r="P13" t="n">
-        <v>17950</v>
+        <v>32100</v>
       </c>
       <c r="Q13" t="n">
-        <v>8120</v>
+        <v>21000</v>
       </c>
       <c r="R13" t="n">
-        <v>276000</v>
+        <v>-81000</v>
       </c>
       <c r="S13" t="n">
-        <v>-68000</v>
+        <v>219000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>키움증권의 매매 행태 및 목표주가 하향 리포트에 대한 의혹 제기. 유리 기판 사업 등 신규 사업 언급.</t>
+          <t>인천공항 이용객 증가 및 내년 영업이익 전망 제시, 합병 효과는 장기적 관점.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['키움증권', '유리 기판']</t>
+          <t>['영업이익', '합병', '인천공항']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31350</v>
+        <v>8490</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.16%</t>
+          <t>'+0.24%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.62</v>
+        <v>0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>58</v>
+        <v>130</v>
       </c>
       <c r="F14" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="G14" t="n">
-        <v>182</v>
+        <v>391</v>
       </c>
       <c r="H14" t="n">
-        <v>52.8</v>
+        <v>26.63</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,91 +1699,91 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>31400</v>
+        <v>8470</v>
       </c>
       <c r="K14" t="n">
-        <v>31500</v>
+        <v>8510</v>
       </c>
       <c r="L14" t="n">
-        <v>32100</v>
+        <v>8870</v>
       </c>
       <c r="M14" t="n">
-        <v>31100</v>
+        <v>8470</v>
       </c>
       <c r="N14" t="n">
-        <v>25.75</v>
+        <v>26.58</v>
       </c>
       <c r="O14" t="n">
-        <v>124581422600</v>
+        <v>31015022555</v>
       </c>
       <c r="P14" t="n">
-        <v>32100</v>
+        <v>17950</v>
       </c>
       <c r="Q14" t="n">
-        <v>21000</v>
+        <v>8120</v>
       </c>
       <c r="R14" t="n">
-        <v>-81000</v>
+        <v>276000</v>
       </c>
       <c r="S14" t="n">
-        <v>219000</v>
+        <v>-68000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>인천공항 이용객 증가 및 내년 영업이익 전망 제시, 합병 효과는 장기적 관점.</t>
+          <t>키움증권의 매매 행태 및 목표주가 하향 리포트에 대한 의혹 제기. 유리 기판 사업 등 신규 사업 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['영업이익', '합병', '인천공항']</t>
+          <t>['키움증권', '유리 기판']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17680</v>
+        <v>3705</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.73%</t>
+          <t>'-0.54%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.76</v>
+        <v>-0.35</v>
       </c>
       <c r="E15" t="n">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="F15" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G15" t="n">
-        <v>992</v>
+        <v>535</v>
       </c>
       <c r="H15" t="n">
-        <v>5.46</v>
+        <v>0.61</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>17810</v>
+        <v>3725</v>
       </c>
       <c r="K15" t="n">
-        <v>17950</v>
+        <v>3740</v>
       </c>
       <c r="L15" t="n">
-        <v>18180</v>
+        <v>4200</v>
       </c>
       <c r="M15" t="n">
-        <v>17410</v>
+        <v>3665</v>
       </c>
       <c r="N15" t="n">
-        <v>6.22</v>
+        <v>0.96</v>
       </c>
       <c r="O15" t="n">
-        <v>148334465410</v>
+        <v>69872623075</v>
       </c>
       <c r="P15" t="n">
-        <v>31500</v>
+        <v>6300</v>
       </c>
       <c r="Q15" t="n">
-        <v>1272</v>
+        <v>1738</v>
       </c>
       <c r="R15" t="n">
-        <v>-273000</v>
+        <v>-176000</v>
       </c>
       <c r="S15" t="n">
-        <v>1000</v>
+        <v>-5000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>추석 연휴 전 2만원 돌파 기대감.  단기 급등 가능성 언급, 실질적 근거 부족.</t>
+          <t>미투온 단기 급락에 대한 부정적 의견 다수. 개잡주 및 상폐 의견.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['2만원 돌파', '기대감', '단기 급등']</t>
+          <t>['단기 급락', '개잡주', '상폐']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3685</v>
+        <v>17700</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.07%</t>
+          <t>'-0.62%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.35</v>
+        <v>-0.76</v>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>155</v>
       </c>
       <c r="F16" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G16" t="n">
-        <v>525</v>
+        <v>1016</v>
       </c>
       <c r="H16" t="n">
-        <v>0.61</v>
+        <v>5.46</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>3725</v>
+        <v>17810</v>
       </c>
       <c r="K16" t="n">
-        <v>3740</v>
+        <v>17950</v>
       </c>
       <c r="L16" t="n">
-        <v>4200</v>
+        <v>18180</v>
       </c>
       <c r="M16" t="n">
-        <v>3665</v>
+        <v>17410</v>
       </c>
       <c r="N16" t="n">
-        <v>0.96</v>
+        <v>6.22</v>
       </c>
       <c r="O16" t="n">
-        <v>69676250665</v>
+        <v>149098131910</v>
       </c>
       <c r="P16" t="n">
-        <v>6300</v>
+        <v>31500</v>
       </c>
       <c r="Q16" t="n">
-        <v>1738</v>
+        <v>1272</v>
       </c>
       <c r="R16" t="n">
-        <v>-176000</v>
+        <v>-273000</v>
       </c>
       <c r="S16" t="n">
-        <v>-5000</v>
+        <v>1000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주가 급락에 대한 불만과 종목 자체에 대한 부정적인 평가. 상폐 가능성 언급.</t>
+          <t>대한광통신 2만원 돌파 기대감. 명절 연휴 후 상승 전망 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주가 급락', '부정적 평가']</t>
+          <t>['2만원 돌파', '쇼티지', '명절 연휴']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1958,13 +1958,13 @@
         <v>0.21</v>
       </c>
       <c r="E17" t="n">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="F17" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="G17" t="n">
-        <v>2391</v>
+        <v>2443</v>
       </c>
       <c r="H17" t="n">
         <v>16.63</v>
@@ -1990,7 +1990,7 @@
         <v>16.42</v>
       </c>
       <c r="O17" t="n">
-        <v>15465662025</v>
+        <v>16176316125</v>
       </c>
       <c r="P17" t="n">
         <v>69200</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31000</v>
+        <v>30950</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-1.90%</t>
+          <t>'-2.06%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.4</v>
       </c>
       <c r="E18" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="F18" t="n">
         <v>45</v>
       </c>
       <c r="G18" t="n">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="H18" t="n">
         <v>11.7</v>
@@ -2082,7 +2082,7 @@
         <v>11.3</v>
       </c>
       <c r="O18" t="n">
-        <v>86051745175</v>
+        <v>87504104875</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>49300</v>
+        <v>49350</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.71%</t>
+          <t>'-3.61%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F19" t="n">
         <v>75</v>
       </c>
       <c r="G19" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H19" t="n">
         <v>38.34</v>
@@ -2174,7 +2174,7 @@
         <v>38.44</v>
       </c>
       <c r="O19" t="n">
-        <v>101803624175</v>
+        <v>105248945075</v>
       </c>
       <c r="P19" t="n">
         <v>67300</v>
@@ -2234,13 +2234,13 @@
         <v>-0.08</v>
       </c>
       <c r="E20" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F20" t="n">
         <v>56</v>
       </c>
       <c r="G20" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H20" t="n">
         <v>1.68</v>
@@ -2266,7 +2266,7 @@
         <v>1.76</v>
       </c>
       <c r="O20" t="n">
-        <v>77051378500</v>
+        <v>77313238000</v>
       </c>
       <c r="P20" t="n">
         <v>39350</v>
@@ -2326,13 +2326,13 @@
         <v>-0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="F21" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G21" t="n">
-        <v>2182</v>
+        <v>2201</v>
       </c>
       <c r="H21" t="n">
         <v>23.03</v>
@@ -2358,7 +2358,7 @@
         <v>23.05</v>
       </c>
       <c r="O21" t="n">
-        <v>355574628900</v>
+        <v>363939483400</v>
       </c>
       <c r="P21" t="n">
         <v>139200</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국형 원전 수주 관련 긍정적 뉴스에도 불구하고 주가 하락세.  재료 소멸 및 투자 심리 위축.</t>
+          <t>한국형 원전 2기 미국 수출 확정, 소형SMR 기대감 있으나 재료 소멸 및 주가 조작 의혹 제기. 외인 숏 포지션 관측.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전 수주', '재료 소멸', '주가 하락']</t>
+          <t>['원전 수출', 'SMR', '주가 조작']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2418,13 +2418,13 @@
         <v>-0.09</v>
       </c>
       <c r="E22" t="n">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F22" t="n">
         <v>133</v>
       </c>
       <c r="G22" t="n">
-        <v>1254</v>
+        <v>1281</v>
       </c>
       <c r="H22" t="n">
         <v>10.38</v>
@@ -2450,7 +2450,7 @@
         <v>10.47</v>
       </c>
       <c r="O22" t="n">
-        <v>160963690185</v>
+        <v>162015391945</v>
       </c>
       <c r="P22" t="n">
         <v>40350</v>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2605</v>
+        <v>2620</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-9.71%</t>
+          <t>'-9.19%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.92</v>
       </c>
       <c r="E23" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F23" t="n">
         <v>59</v>
       </c>
       <c r="G23" t="n">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="H23" t="n">
         <v>1.4</v>
@@ -2542,7 +2542,7 @@
         <v>0.48</v>
       </c>
       <c r="O23" t="n">
-        <v>23504235006</v>
+        <v>23586482046</v>
       </c>
       <c r="P23" t="n">
         <v>4760</v>

--- a/data/trending_integrated_20260923_15.xlsx
+++ b/data/trending_integrated_20260923_15.xlsx
@@ -578,13 +578,13 @@
         <v>-1.02</v>
       </c>
       <c r="E2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G2" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H2" t="n">
         <v>1.63</v>
@@ -610,7 +610,7 @@
         <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>51299222831</v>
+        <v>51310448731</v>
       </c>
       <c r="P2" t="n">
         <v>6950</v>
@@ -670,13 +670,13 @@
         <v>-0.5</v>
       </c>
       <c r="E3" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F3" t="n">
         <v>92</v>
       </c>
       <c r="G3" t="n">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="H3" t="n">
         <v>0.6</v>
@@ -702,7 +702,7 @@
         <v>1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>132392802770</v>
+        <v>132404640570</v>
       </c>
       <c r="P3" t="n">
         <v>34650</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>NASA 선정 초소형 엑스레이 발생기 'Xcam6' 및 스페이스X 관련 소식. 포터블 X-Ray 시장 성장 기대.</t>
+          <t>NASA 및 스페이스X 선정, 11조원 규모 포터블 X-Ray 시장 진출 가능성. 기술력 기반 실적 성장 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['NASA', '스페이스X']</t>
+          <t>['X-Ray', '스페이스X']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>-0.39</v>
       </c>
       <c r="E4" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F4" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G4" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="H4" t="n">
         <v>1.02</v>
@@ -794,7 +794,7 @@
         <v>1.41</v>
       </c>
       <c r="O4" t="n">
-        <v>67544255732</v>
+        <v>67585626116</v>
       </c>
       <c r="P4" t="n">
         <v>2465</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈, 美 특허 플렉시블PCB AI 데이터센터향 공급 확대. 엔비디아 ESS 파트너 선정.</t>
+          <t>미국 특허(플렉시블 PCB) 및 AI 데이터센터, ESS 관련 사업 강화 기대감. 엔비디아 및 LG엔솔 관련 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['플렉시블 PCB', 'AI 데이터센터', 'ESS']</t>
+          <t>['ESS', 'AI 데이터센터']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -860,7 +860,7 @@
         <v>142</v>
       </c>
       <c r="G5" t="n">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H5" t="n">
         <v>0.62</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>314403425010</v>
+        <v>314421535690</v>
       </c>
       <c r="P5" t="n">
         <v>30550</v>
@@ -946,13 +946,13 @@
         <v>0.42</v>
       </c>
       <c r="E6" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F6" t="n">
         <v>55</v>
       </c>
       <c r="G6" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H6" t="n">
         <v>0.86</v>
@@ -978,7 +978,7 @@
         <v>0.44</v>
       </c>
       <c r="O6" t="n">
-        <v>173384362825</v>
+        <v>173396702625</v>
       </c>
       <c r="P6" t="n">
         <v>25700</v>
@@ -1041,10 +1041,10 @@
         <v>148</v>
       </c>
       <c r="F7" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H7" t="n">
         <v>1.89</v>
@@ -1070,7 +1070,7 @@
         <v>2.79</v>
       </c>
       <c r="O7" t="n">
-        <v>131520875400</v>
+        <v>131532695670</v>
       </c>
       <c r="P7" t="n">
         <v>64600</v>
@@ -1130,13 +1130,13 @@
         <v>0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F8" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G8" t="n">
-        <v>531</v>
+        <v>547</v>
       </c>
       <c r="H8" t="n">
         <v>75.51000000000001</v>
@@ -1162,7 +1162,7 @@
         <v>75.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1129935170000</v>
+        <v>1132818490000</v>
       </c>
       <c r="P8" t="n">
         <v>243500</v>
@@ -1254,7 +1254,7 @@
         <v>2.32</v>
       </c>
       <c r="O9" t="n">
-        <v>92792445195</v>
+        <v>92805844735</v>
       </c>
       <c r="P9" t="n">
         <v>16200</v>
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="G10" t="n">
-        <v>1793</v>
+        <v>1853</v>
       </c>
       <c r="H10" t="n">
         <v>46.55</v>
@@ -1346,7 +1346,7 @@
         <v>46.56</v>
       </c>
       <c r="O10" t="n">
-        <v>5279657049750</v>
+        <v>5279842910250</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>삼성전자 주가 30만 돌파 및 9월, 10월 예상 주가 전망. 외인 기관 쌍끌이 매수 관측.</t>
+          <t>대선 관련 정치적 발언과 함께 주가 상승 기대감 표출. 외인·기관 쌍끌이 매수 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['주가 전망', '외인 매수', '쌍끌이']</t>
+          <t>['반도체 랠리', '외인기관']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1406,10 +1406,10 @@
         <v>-0.16</v>
       </c>
       <c r="E11" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G11" t="n">
         <v>239</v>
@@ -1438,7 +1438,7 @@
         <v>9.77</v>
       </c>
       <c r="O11" t="n">
-        <v>104059164975</v>
+        <v>104072668575</v>
       </c>
       <c r="P11" t="n">
         <v>23550</v>
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="G12" t="n">
-        <v>1707</v>
+        <v>1770</v>
       </c>
       <c r="H12" t="n">
         <v>50.15</v>
@@ -1530,7 +1530,7 @@
         <v>50.17</v>
       </c>
       <c r="O12" t="n">
-        <v>5211081479000</v>
+        <v>5211615873000</v>
       </c>
       <c r="P12" t="n">
         <v>2987000</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>ADR 대비 부진한 주가 흐름에 대한 불만 고조.  증권사 및 정부 정책 비판.</t>
+          <t>정부 정책 및 외국인 매매에 대한 불만 속에서 주가 부진에 대한 답답함 표출. 자사주 매입 기대감 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['ADR', '주가 관리', '불만']</t>
+          <t>['ADR', '자사주 매입']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1596,7 +1596,7 @@
         <v>36</v>
       </c>
       <c r="G13" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H13" t="n">
         <v>52.81</v>
@@ -1622,7 +1622,7 @@
         <v>25.75</v>
       </c>
       <c r="O13" t="n">
-        <v>127118999600</v>
+        <v>127176613100</v>
       </c>
       <c r="P13" t="n">
         <v>32100</v>
@@ -1682,13 +1682,13 @@
         <v>0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F14" t="n">
         <v>55</v>
       </c>
       <c r="G14" t="n">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="H14" t="n">
         <v>26.63</v>
@@ -1714,7 +1714,7 @@
         <v>26.58</v>
       </c>
       <c r="O14" t="n">
-        <v>31015022555</v>
+        <v>31026823655</v>
       </c>
       <c r="P14" t="n">
         <v>17950</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>키움증권의 매매 행태 및 목표주가 하향 리포트에 대한 의혹 제기. 유리 기판 사업 등 신규 사업 언급.</t>
+          <t>주가 조작 및 허수 매도에 대한 불만과 함께, 신규 사업(유리 기판) 및 실적 개선 가능성 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['키움증권', '유리 기판']</t>
+          <t>['유리기판', '실적']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1774,13 +1774,13 @@
         <v>-0.35</v>
       </c>
       <c r="E15" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F15" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G15" t="n">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="H15" t="n">
         <v>0.61</v>
@@ -1806,7 +1806,7 @@
         <v>0.96</v>
       </c>
       <c r="O15" t="n">
-        <v>69872623075</v>
+        <v>69873497455</v>
       </c>
       <c r="P15" t="n">
         <v>6300</v>
@@ -1866,13 +1866,13 @@
         <v>-0.76</v>
       </c>
       <c r="E16" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F16" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G16" t="n">
-        <v>1016</v>
+        <v>1034</v>
       </c>
       <c r="H16" t="n">
         <v>5.46</v>
@@ -1898,7 +1898,7 @@
         <v>6.22</v>
       </c>
       <c r="O16" t="n">
-        <v>149098131910</v>
+        <v>149216633410</v>
       </c>
       <c r="P16" t="n">
         <v>31500</v>
@@ -1958,13 +1958,13 @@
         <v>0.21</v>
       </c>
       <c r="E17" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="F17" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="G17" t="n">
-        <v>2443</v>
+        <v>2522</v>
       </c>
       <c r="H17" t="n">
         <v>16.63</v>
@@ -1990,7 +1990,7 @@
         <v>16.42</v>
       </c>
       <c r="O17" t="n">
-        <v>16176316125</v>
+        <v>16176927125</v>
       </c>
       <c r="P17" t="n">
         <v>69200</v>
@@ -2056,7 +2056,7 @@
         <v>45</v>
       </c>
       <c r="G18" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H18" t="n">
         <v>11.7</v>
@@ -2082,7 +2082,7 @@
         <v>11.3</v>
       </c>
       <c r="O18" t="n">
-        <v>87504104875</v>
+        <v>87540873475</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2142,13 +2142,13 @@
         <v>-0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F19" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G19" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H19" t="n">
         <v>38.34</v>
@@ -2174,7 +2174,7 @@
         <v>38.44</v>
       </c>
       <c r="O19" t="n">
-        <v>105248945075</v>
+        <v>105275396675</v>
       </c>
       <c r="P19" t="n">
         <v>67300</v>
@@ -2234,10 +2234,10 @@
         <v>-0.08</v>
       </c>
       <c r="E20" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F20" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G20" t="n">
         <v>159</v>
@@ -2266,7 +2266,7 @@
         <v>1.76</v>
       </c>
       <c r="O20" t="n">
-        <v>77313238000</v>
+        <v>77325516250</v>
       </c>
       <c r="P20" t="n">
         <v>39350</v>
@@ -2326,13 +2326,13 @@
         <v>-0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>743</v>
+        <v>754</v>
       </c>
       <c r="F21" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="G21" t="n">
-        <v>2201</v>
+        <v>2251</v>
       </c>
       <c r="H21" t="n">
         <v>23.03</v>
@@ -2358,7 +2358,7 @@
         <v>23.05</v>
       </c>
       <c r="O21" t="n">
-        <v>363939483400</v>
+        <v>363953454100</v>
       </c>
       <c r="P21" t="n">
         <v>139200</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>한국형 원전 2기 미국 수출 확정, 소형SMR 기대감 있으나 재료 소멸 및 주가 조작 의혹 제기. 외인 숏 포지션 관측.</t>
+          <t>미국 원전 수출 관련 호재 언급에도 불구하고 주가 하락에 대한 불안감과 불신 표출.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전 수출', 'SMR', '주가 조작']</t>
+          <t>['원전', 'SMR']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2418,13 +2418,13 @@
         <v>-0.09</v>
       </c>
       <c r="E22" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F22" t="n">
         <v>133</v>
       </c>
       <c r="G22" t="n">
-        <v>1281</v>
+        <v>1302</v>
       </c>
       <c r="H22" t="n">
         <v>10.38</v>
@@ -2450,7 +2450,7 @@
         <v>10.47</v>
       </c>
       <c r="O22" t="n">
-        <v>162015391945</v>
+        <v>162032709865</v>
       </c>
       <c r="P22" t="n">
         <v>40350</v>
@@ -2510,13 +2510,13 @@
         <v>0.92</v>
       </c>
       <c r="E23" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F23" t="n">
         <v>59</v>
       </c>
       <c r="G23" t="n">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="H23" t="n">
         <v>1.4</v>
@@ -2542,7 +2542,7 @@
         <v>0.48</v>
       </c>
       <c r="O23" t="n">
-        <v>23586482046</v>
+        <v>23605118106</v>
       </c>
       <c r="P23" t="n">
         <v>4760</v>
